--- a/Pics & Schematics/Billing/Biling.xlsx
+++ b/Pics & Schematics/Billing/Biling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\StealthDucky\Pics &amp; Schematics\Billing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF77E461-2338-4583-A30D-AA9EF928F931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985660A7-D5CB-45B4-9009-7A9AAEAD8F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,21 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Vendor</t>
-  </si>
-  <si>
-    <t>JLCPCB</t>
-  </si>
-  <si>
-    <t>DIGIKEY</t>
-  </si>
-  <si>
-    <t>ROBU</t>
-  </si>
-  <si>
-    <t>ELECTROPI</t>
   </si>
   <si>
     <t>Price (IN RUPPES)</t>
@@ -63,6 +51,12 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>JLC COMPONENTS</t>
+  </si>
+  <si>
+    <t>JLCPCBA</t>
   </si>
 </sst>
 </file>
@@ -92,7 +86,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -131,16 +125,78 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -148,133 +204,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -287,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -295,7 +224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -304,31 +233,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -611,87 +525,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>6</v>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9">
-        <v>11281.7</v>
-      </c>
-      <c r="C2" s="10">
-        <f>B2*0.011</f>
-        <v>124.09869999999999</v>
+      <c r="A2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <f>C2/0.011</f>
+        <v>6621.8181818181829</v>
+      </c>
+      <c r="C2" s="4">
+        <v>72.84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
+    <row r="3" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>7077.64</v>
-      </c>
-      <c r="C3" s="5">
-        <f t="shared" ref="C3:C5" si="0">B3*0.011</f>
-        <v>77.854039999999998</v>
+        <f>C3/0.011</f>
+        <v>9686.363636363636</v>
+      </c>
+      <c r="C3" s="4">
+        <v>106.55</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>532.25</v>
-      </c>
-      <c r="C4" s="5">
-        <f t="shared" si="0"/>
-        <v>5.8547499999999992</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3">
-        <v>404.74</v>
-      </c>
-      <c r="C5" s="7">
-        <f t="shared" si="0"/>
-        <v>4.45214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="11">
-        <f>SUM(C2:C5)</f>
-        <v>212.25963000000002</v>
+      <c r="B4" s="9"/>
+      <c r="C4" s="6">
+        <f>SUM(C2:C3)</f>
+        <v>179.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
